--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00695B-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00695B-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0703FE71-6647-4186-B8E5-AAAA2FB8E7C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0B151E61-D1EF-4050-B90C-2A24D709F8FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{7C52883A-4F56-47C1-A6B3-B5ABA24C57CA}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{15264995-57BF-490E-AB5D-97418ACA31DF}"/>
   </bookViews>
   <sheets>
     <sheet name="00695B-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1642,25 +1642,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F992DAB6-1028-406A-A0D1-108672EF4E99}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5089FA3-CD3F-421E-8726-29FEF790A8B9}">
   <dimension ref="A1:R48"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1688,7 +1688,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1718,7 +1718,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1764,7 +1764,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1814,7 +1814,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1868,7 +1868,7 @@
         <v>2.94</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1894,7 +1894,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1950,7 +1950,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>2025</v>
       </c>
@@ -2004,7 +2004,7 @@
         <v>3.12</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -2060,7 +2060,7 @@
         <v>0.74</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -2116,7 +2116,7 @@
         <v>0.81</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>27</v>
       </c>
@@ -2172,7 +2172,7 @@
         <v>0.73</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>27</v>
       </c>
@@ -2228,7 +2228,7 @@
         <v>0.84</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="51">
         <v>2024</v>
       </c>
@@ -2282,7 +2282,7 @@
         <v>2.4300000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>27</v>
       </c>
@@ -2338,7 +2338,7 @@
         <v>0.65</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>27</v>
       </c>
@@ -2394,7 +2394,7 @@
         <v>0.69</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>27</v>
       </c>
@@ -2450,7 +2450,7 @@
         <v>0.59</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>27</v>
       </c>
@@ -2506,7 +2506,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="49">
         <v>2023</v>
       </c>
@@ -2560,7 +2560,7 @@
         <v>1.57</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>27</v>
       </c>
@@ -2616,7 +2616,7 @@
         <v>0.49</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>27</v>
       </c>
@@ -2672,7 +2672,7 @@
         <v>0.42</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>27</v>
       </c>
@@ -2728,7 +2728,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>27</v>
       </c>
@@ -2784,7 +2784,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="51">
         <v>2022</v>
       </c>
@@ -2838,7 +2838,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>27</v>
       </c>
@@ -2894,7 +2894,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>27</v>
       </c>
@@ -2950,7 +2950,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>27</v>
       </c>
@@ -3006,7 +3006,7 @@
         <v>0.24</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
         <v>27</v>
       </c>
@@ -3062,7 +3062,7 @@
         <v>0.25</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="49">
         <v>2021</v>
       </c>
@@ -3116,7 +3116,7 @@
         <v>1.29</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
         <v>27</v>
       </c>
@@ -3172,7 +3172,7 @@
         <v>0.28000000000000003</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="19" t="s">
         <v>27</v>
       </c>
@@ -3228,7 +3228,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
         <v>27</v>
       </c>
@@ -3284,7 +3284,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
         <v>27</v>
       </c>
@@ -3340,7 +3340,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="51">
         <v>2020</v>
       </c>
@@ -3394,7 +3394,7 @@
         <v>1.66</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
         <v>27</v>
       </c>
@@ -3450,7 +3450,7 @@
         <v>0.36</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
         <v>27</v>
       </c>
@@ -3506,7 +3506,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>27</v>
       </c>
@@ -3562,7 +3562,7 @@
         <v>0.53</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>27</v>
       </c>
@@ -3618,7 +3618,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="49">
         <v>2019</v>
       </c>
@@ -3672,7 +3672,7 @@
         <v>7.62</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
         <v>27</v>
       </c>
@@ -3728,7 +3728,7 @@
         <v>0.66</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
         <v>27</v>
       </c>
@@ -3784,7 +3784,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
         <v>27</v>
       </c>
@@ -3840,7 +3840,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="19" t="s">
         <v>27</v>
       </c>
@@ -3896,7 +3896,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="51">
         <v>2018</v>
       </c>
@@ -3950,7 +3950,7 @@
         <v>1.36</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
         <v>27</v>
       </c>
@@ -4006,7 +4006,7 @@
         <v>0.46</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
         <v>27</v>
       </c>
@@ -4062,7 +4062,7 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
         <v>27</v>
       </c>
@@ -4118,7 +4118,7 @@
         <v>0.06</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
         <v>27</v>
       </c>
@@ -4174,7 +4174,7 @@
         <v>0.56999999999999995</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="49" t="s">
         <v>85</v>
       </c>
